--- a/tables/Table 1 Covariate summary.xlsx
+++ b/tables/Table 1 Covariate summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\OSM_red_squirrel_distribution\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2714D502-12E7-4470-BD00-11913D668B39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5611BE67-FC00-4E6A-9582-5E41E19074D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="2676" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -208,9 +208,6 @@
     <t>71.19 (13.86–279.67)</t>
   </si>
   <si>
-    <t>Cumulative Disturbance</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sum of the footprint of all anthropogenic disturbances in the surrounding matrix. </t>
   </si>
   <si>
@@ -224,6 +221,9 @@
   </si>
   <si>
     <t xml:space="preserve">Proportion cover of mixedwood forest. (Neither &gt;75% broadleaf nor &gt;75% mixedwood canopy cover). </t>
+  </si>
+  <si>
+    <t>Cumulative Footprint</t>
   </si>
 </sst>
 </file>
@@ -684,19 +684,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="2.85546875" customWidth="1"/>
+    <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.88671875" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
     <col min="5" max="5" width="21" customWidth="1"/>
     <col min="6" max="6" width="87" customWidth="1"/>
-    <col min="7" max="7" width="2.5703125" customWidth="1"/>
+    <col min="7" max="7" width="2.5546875" customWidth="1"/>
     <col min="9" max="9" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="5"/>
@@ -705,7 +705,7 @@
       <c r="F1" s="5"/>
       <c r="G1" s="2"/>
     </row>
-    <row r="2" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="4"/>
@@ -716,7 +716,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="14" t="s">
@@ -735,7 +735,7 @@
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="15" t="s">
@@ -748,7 +748,7 @@
       <c r="F4" s="17"/>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
@@ -763,7 +763,7 @@
       </c>
       <c r="G5" s="4"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="s">
@@ -774,11 +774,11 @@
         <v>42</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G6" s="2"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="3" t="s">
@@ -789,11 +789,11 @@
         <v>48</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G7" s="2"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="3" t="s">
@@ -808,7 +808,7 @@
       </c>
       <c r="G8" s="2"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="3" t="s">
@@ -819,11 +819,11 @@
         <v>50</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G9" s="2"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="3" t="s">
@@ -838,7 +838,7 @@
       </c>
       <c r="G10" s="2"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="3" t="s">
@@ -853,7 +853,7 @@
       </c>
       <c r="G11" s="2"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="3" t="s">
@@ -868,35 +868,35 @@
       </c>
       <c r="G12" s="2"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="15" t="s">
         <v>22</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E13" s="18"/>
       <c r="F13" s="17"/>
       <c r="G13" s="4"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="3" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D14" s="10"/>
       <c r="E14" s="2" t="s">
         <v>45</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G14" s="2"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="3" t="s">
@@ -911,7 +911,7 @@
       </c>
       <c r="G15" s="2"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="3" t="s">
@@ -926,7 +926,7 @@
       </c>
       <c r="G16" s="2"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="3" t="s">
@@ -941,7 +941,7 @@
       </c>
       <c r="G17" s="2"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="3" t="s">
@@ -956,7 +956,7 @@
       </c>
       <c r="G18" s="2"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="3" t="s">
@@ -971,7 +971,7 @@
       </c>
       <c r="G19" s="2"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="3" t="s">
@@ -986,7 +986,7 @@
       </c>
       <c r="G20" s="2"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="7" t="s">
@@ -1001,20 +1001,20 @@
       </c>
       <c r="G21" s="2"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="15" t="s">
         <v>23</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E22" s="19"/>
       <c r="F22" s="19"/>
       <c r="G22" s="2"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="3" t="s">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="G23" s="2"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="3" t="s">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="G24" s="2"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="3" t="s">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="G25" s="2"/>
     </row>
-    <row r="26" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="6" t="s">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G26" s="2"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -1083,7 +1083,7 @@
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -1092,7 +1092,7 @@
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -1101,7 +1101,7 @@
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -1110,7 +1110,7 @@
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>

--- a/tables/Table 1 Covariate summary.xlsx
+++ b/tables/Table 1 Covariate summary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\OSM_red_squirrel_distribution\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5611BE67-FC00-4E6A-9582-5E41E19074D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9714D421-0D6F-4685-A737-DE7DA165C730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="2676" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -684,19 +684,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="2.88671875" customWidth="1"/>
+    <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.85546875" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
     <col min="5" max="5" width="21" customWidth="1"/>
     <col min="6" max="6" width="87" customWidth="1"/>
-    <col min="7" max="7" width="2.5546875" customWidth="1"/>
+    <col min="7" max="7" width="2.5703125" customWidth="1"/>
     <col min="9" max="9" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="5"/>
@@ -705,7 +705,7 @@
       <c r="F1" s="5"/>
       <c r="G1" s="2"/>
     </row>
-    <row r="2" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="4"/>
@@ -716,7 +716,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="14" t="s">
@@ -735,7 +735,7 @@
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="15" t="s">
@@ -748,7 +748,7 @@
       <c r="F4" s="17"/>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
@@ -763,7 +763,7 @@
       </c>
       <c r="G5" s="4"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="s">
@@ -778,7 +778,7 @@
       </c>
       <c r="G6" s="2"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="3" t="s">
@@ -793,7 +793,7 @@
       </c>
       <c r="G7" s="2"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="3" t="s">
@@ -808,7 +808,7 @@
       </c>
       <c r="G8" s="2"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="3" t="s">
@@ -823,7 +823,7 @@
       </c>
       <c r="G9" s="2"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="3" t="s">
@@ -838,7 +838,7 @@
       </c>
       <c r="G10" s="2"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="3" t="s">
@@ -853,7 +853,7 @@
       </c>
       <c r="G11" s="2"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="3" t="s">
@@ -868,7 +868,7 @@
       </c>
       <c r="G12" s="2"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="15" t="s">
@@ -881,7 +881,7 @@
       <c r="F13" s="17"/>
       <c r="G13" s="4"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="3" t="s">
@@ -896,7 +896,7 @@
       </c>
       <c r="G14" s="2"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="3" t="s">
@@ -911,7 +911,7 @@
       </c>
       <c r="G15" s="2"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="3" t="s">
@@ -926,7 +926,7 @@
       </c>
       <c r="G16" s="2"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="3" t="s">
@@ -941,7 +941,7 @@
       </c>
       <c r="G17" s="2"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="3" t="s">
@@ -956,7 +956,7 @@
       </c>
       <c r="G18" s="2"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="3" t="s">
@@ -971,7 +971,7 @@
       </c>
       <c r="G19" s="2"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="3" t="s">
@@ -986,7 +986,7 @@
       </c>
       <c r="G20" s="2"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="7" t="s">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="G21" s="2"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="15" t="s">
@@ -1014,7 +1014,7 @@
       <c r="F22" s="19"/>
       <c r="G22" s="2"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="3" t="s">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="G23" s="2"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="3" t="s">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="G24" s="2"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="3" t="s">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="G25" s="2"/>
     </row>
-    <row r="26" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="6" t="s">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G26" s="2"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -1083,7 +1083,7 @@
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -1092,7 +1092,7 @@
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -1101,7 +1101,7 @@
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -1110,7 +1110,7 @@
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
